--- a/public/word_upload_template.xlsx
+++ b/public/word_upload_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5B8915-8FBB-42B4-BD5A-003F7ED8F187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB035E44-7083-4260-BBF1-92A9D8B56A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A30AAC7C-46B1-49FE-8262-C4C7D5606DC2}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" xr2:uid="{A30AAC7C-46B1-49FE-8262-C4C7D5606DC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>english_word</t>
   </si>
@@ -49,6 +49,27 @@
   </si>
   <si>
     <t>class</t>
+  </si>
+  <si>
+    <t>valo</t>
+  </si>
+  <si>
+    <t>noun</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>Pre-Primary1, class 1</t>
+  </si>
+  <si>
+    <t>english_meaning</t>
+  </si>
+  <si>
+    <t>english_meaning33</t>
+  </si>
+  <si>
+    <t>sadafrwr</t>
   </si>
 </sst>
 </file>
@@ -400,10 +421,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4033987-AE01-48FC-B368-CDF151EE811F}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="22.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -411,13 +432,36 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/public/word_upload_template.xlsx
+++ b/public/word_upload_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t xml:space="preserve">english_word</t>
   </si>
@@ -49,6 +49,9 @@
     <t xml:space="preserve">antonyms</t>
   </si>
   <si>
+    <t xml:space="preserve">Example-word</t>
+  </si>
+  <si>
     <t xml:space="preserve">exmple-word</t>
   </si>
   <si>
@@ -71,6 +74,9 @@
   </si>
   <si>
     <t xml:space="preserve">less, not regular, many</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example-word2</t>
   </si>
   <si>
     <t xml:space="preserve">Exmple-word2</t>
@@ -399,57 +405,57 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/public/word_upload_template.xlsx
+++ b/public/word_upload_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t xml:space="preserve">english_word</t>
   </si>
@@ -74,21 +74,6 @@
   </si>
   <si>
     <t xml:space="preserve">less, not regular, many</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example-word2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exmple-word2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exmple-word meaning2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">some2, many2, regular2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">less2, not regular2, many2</t>
   </si>
 </sst>
 </file>
@@ -368,7 +353,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultColWidth="22.21875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -429,35 +414,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/public/word_upload_template.xlsx
+++ b/public/word_upload_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t xml:space="preserve">english_word</t>
   </si>
@@ -31,12 +31,12 @@
     <t xml:space="preserve">english_meaning</t>
   </si>
   <si>
+    <t xml:space="preserve">phonetics</t>
+  </si>
+  <si>
     <t xml:space="preserve">part_of_speech</t>
   </si>
   <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
     <t xml:space="preserve">class</t>
   </si>
   <si>
@@ -49,7 +49,7 @@
     <t xml:space="preserve">antonyms</t>
   </si>
   <si>
-    <t xml:space="preserve">Example-word</t>
+    <t xml:space="preserve">Example-word-2</t>
   </si>
   <si>
     <t xml:space="preserve">exmple-word</t>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t xml:space="preserve">noun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test</t>
   </si>
   <si>
     <t xml:space="preserve">Pre-Primary1, class 1</t>
@@ -83,7 +80,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,12 +102,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -160,7 +151,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -353,40 +344,40 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1048576"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="22.21875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -395,26 +386,25 @@
       <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="0" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
